--- a/outputs/email/nih_surgery_benchmark_comparison.xlsx
+++ b/outputs/email/nih_surgery_benchmark_comparison.xlsx
@@ -9,8 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blue Ridge FY2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MGH self-reported" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External calibration" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full ranking FY21-25" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104" customWidth="1" min="1" max="1"/>
@@ -489,7 +491,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Prepared 5 August 2026.  Source: NIH ExPORTER FY2021-FY2025 (archived, checksummed).</t>
+          <t>Prepared 5 August 2026.  Every figure traceable to a named source; see the Sources tab.</t>
         </is>
       </c>
     </row>
@@ -506,79 +508,79 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SHEET 1  Blue Ridge FY2025 - every institution in the Blue Ridge FY2025 departments-of-surgery table,</t>
+          <t>TABS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         beside the figure this analysis produces, plus the hospitals Blue Ridge does not cover.</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">         55 of the 75 Blue Ridge institutions agree to the dollar; 60 agree to within 1%.</t>
+          <t>Blue Ridge FY2025      Every institution in the BRIMR FY2025 departments-of-surgery table beside the</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Green = agrees to the dollar.  Amber = reconstructed hospital, no Blue Ridge line exists.</t>
+          <t xml:space="preserve">                       figure this analysis produces, plus the hospitals BRIMR does not cover.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       55 of BRIMR's 75 agree to the dollar; 60 agree to within 1%.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SHEET 2  MGH self-reported - the MGH Department of Surgery figures published on massgeneral.org,</t>
+          <t xml:space="preserve">                       Green = agrees to the dollar.  Amber = reconstructed hospital, no BRIMR line.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         beside this analysis. 87.9% agreement on NIH, independently derived.</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>External calibration   The two places an outside number exists to check the reconstruction against:</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SHEET 3  Full ranking FY2021-FY2025 - all 119 ranked departments, both ways of counting a grant.</t>
+          <t xml:space="preserve">                       MGH's own published figures, and BRIMR's Vanderbilt line.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         A rank in (parentheses) is a multi-hospital roll-up shown where it would fall as one</t>
-        </is>
-      </c>
+      <c r="A15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">         department; it holds no place in the ranking itself.</t>
+          <t>Full ranking FY21-25   All 119 ranked departments, both ways of counting a grant.  A rank in</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr"/>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       (parentheses) is a multi-hospital roll-up shown where it would fall as one</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>TWO THINGS TO KNOW WHEN READING THESE NUMBERS</t>
+          <t xml:space="preserve">                       department; it holds no place in the ranking itself.</t>
         </is>
       </c>
     </row>
@@ -588,35 +590,31 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>1. Blue Ridge assigns a department only where NIH does, and NIH department-codes universities only.</t>
+          <t>Claim verification     88 numeric claims re-derived from the published tables, each beside the file</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">   No hospital appears anywhere in their surgery table. MGH, BWH, Memorial Sloan Kettering, Boston</t>
+          <t xml:space="preserve">                       it came from.  Regenerate with:</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Children's and 23 other uncoded recipients are reconstructed here from dated PubMed author</t>
+          <t xml:space="preserve">                         python3 docs/validation/verify_email_claims.py</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   affiliations. Those rows are marked and are lower bounds, not like-for-like with an NIH-coded</t>
-        </is>
-      </c>
+      <c r="A23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">   figure.</t>
+          <t>Sources                Checksums, URLs and retrieval dates for everything above.</t>
         </is>
       </c>
     </row>
@@ -626,28 +624,90 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2. A grant and an award-year are different counts. A grant is one project counted once; an award-year</t>
+          <t>TWO THINGS TO KNOW WHEN READING THESE NUMBERS</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   is that grant counted once for each fiscal year it was funded, so a five-year grant contributes</t>
-        </is>
-      </c>
+      <c r="A27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">   five. Nationally there are 2.65 award-years per grant, and the two rank institutions differently.</t>
+          <t>1. BRIMR assigns a department only where NIH does, and NIH department-codes universities only.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Both are given.</t>
+          <t xml:space="preserve">   No hospital appears anywhere in their surgery table. MGH, BWH, Memorial Sloan Kettering, Boston</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Children's and 15 other uncoded recipients are reconstructed here from dated PubMed author</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   affiliations. Those rows are marked and are lower bounds, not like-for-like with an NIH-coded</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   figure. Measured against the two outside numbers that exist, the reconstruction recovers 87.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (MGH) and 77.7% (Vanderbilt) — most of the money, never all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>2. A grant and an award-year are different counts. A grant is one project counted once; an award-year</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   is that grant counted once for each fiscal year it was funded, so a five-year grant contributes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   five. Nationally there are 2.65 award-years per grant, and the two rank institutions differently:</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   MGB leads on R01 award-years (179 to Michigan's 165) and is second on distinct R01 grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (56 to Michigan's 59). Both are given throughout.</t>
         </is>
       </c>
     </row>
@@ -662,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -673,9 +733,11 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="64" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Institution</t>
@@ -714,6 +776,16 @@
       <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Agrees to the dollar</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Blue Ridge source</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>This analysis source</t>
         </is>
       </c>
     </row>
@@ -748,6 +820,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -780,6 +862,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -812,6 +904,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -844,6 +946,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -876,6 +988,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -908,6 +1030,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -940,6 +1072,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -972,6 +1114,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1004,6 +1156,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1036,6 +1198,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1068,6 +1240,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1100,6 +1282,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1132,6 +1324,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1164,6 +1366,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1196,6 +1408,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1228,6 +1450,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1260,6 +1492,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1292,6 +1534,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1324,6 +1576,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1356,6 +1618,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1388,6 +1660,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1420,6 +1702,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1452,6 +1744,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1484,6 +1786,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1516,6 +1828,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1548,6 +1870,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1580,6 +1912,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1612,6 +1954,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1644,6 +1996,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1676,6 +2038,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1708,6 +2080,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1740,6 +2122,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1772,6 +2164,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1804,6 +2206,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1836,6 +2248,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1868,6 +2290,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1900,6 +2332,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1932,6 +2374,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1964,6 +2416,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1996,6 +2458,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2028,6 +2500,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2060,6 +2542,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2092,6 +2584,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2124,6 +2626,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2156,6 +2668,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2188,6 +2710,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2220,6 +2752,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2252,6 +2794,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2284,6 +2836,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2316,6 +2878,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2348,6 +2920,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2380,6 +2962,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2412,6 +3004,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2444,6 +3046,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2476,6 +3088,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2508,6 +3130,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -2540,6 +3172,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2572,6 +3214,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2604,6 +3256,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -2636,6 +3298,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -2668,6 +3340,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -2700,6 +3382,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2732,6 +3424,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -2764,6 +3466,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -2796,6 +3508,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -2828,6 +3550,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -2860,6 +3592,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -2892,6 +3634,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -2924,6 +3676,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -2956,6 +3718,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -2986,6 +3758,16 @@
       <c r="H72" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
         </is>
       </c>
     </row>
@@ -3014,6 +3796,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J73" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3046,6 +3838,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -3078,6 +3880,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3108,6 +3920,16 @@
       <c r="H76" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>BRIMR 2025 rankings, Surgery table</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
         </is>
       </c>
     </row>
@@ -3134,6 +3956,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -3158,6 +3990,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -3182,6 +4024,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -3206,6 +4058,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -3230,6 +4092,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3254,6 +4126,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I82" s="1" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J82" s="1" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025, ORG_DEPT = SURGERY</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -3278,6 +4160,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -3302,6 +4194,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -3326,6 +4228,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -3350,6 +4262,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -3374,6 +4296,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -3398,6 +4330,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -3422,6 +4364,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -3446,6 +4398,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -3470,6 +4432,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -3494,6 +4466,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -3518,6 +4500,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -3542,6 +4534,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -3566,6 +4568,16 @@
           <t>n/a — not in Blue Ridge</t>
         </is>
       </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J95" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -3588,6 +4600,16 @@
       <c r="H96" s="8" t="inlineStr">
         <is>
           <t>n/a — not in Blue Ridge</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>not in the BRIMR surgery table</t>
+        </is>
+      </c>
+      <c r="J96" s="8" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER FY2025 + PubMed affiliation reconstruction (lower bound)</t>
         </is>
       </c>
     </row>
@@ -3602,19 +4624,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="64" customWidth="1" min="8" max="8"/>
+    <col width="64" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Department</t>
@@ -3632,7 +4656,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Published by MGH ($)</t>
+          <t>Published figure ($)</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -3646,6 +4670,16 @@
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Published source</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>This analysis source</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -3676,7 +4710,17 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>MGH reports expenditures drawn down in the year; this analysis sums awards obligated in FY2024. Reconstructed from PubMed affiliations, so a lower bound.</t>
+          <t>massgeneral.org/surgery/research — "Our research program in 2024"</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>reconstructed FY2024 awards, data/processed/pi_departments.parquet</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>MGH reports expenditures drawn down during the year; this analysis sums awards obligated in FY2024. Reconstructed from PubMed affiliations, so a lower bound.</t>
         </is>
       </c>
     </row>
@@ -3701,7 +4745,17 @@
       <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>Out of scope. NIH is 47% of it; DOD and other federal add $10M, royalties $6M. No NIH-based ranking sees the other $39M.</t>
+          <t>massgeneral.org/surgery/research</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>out of scope</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>NIH is 47% of it. DOD and other federal add $10M, royalties $6M. No NIH-based ranking sees the other $39M.</t>
         </is>
       </c>
     </row>
@@ -3726,7 +4780,56 @@
       <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Out of scope: this analysis counts NIH only.</t>
+          <t>massgeneral.org/surgery/research</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>out of scope</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>This analysis counts NIH only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Vanderbilt University Medical Center</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>NIH funding, surgery</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>14408389</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>11195258</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>BRIMR 2025, reported under "Vanderbilt University"</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>$336,630 NIH-coded at the university + $10,858,628 reconstructed at VUMC</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>The second calibration, from the opposite direction. NIH codes no department for VUMC at all: 524 awards, $451.6M in FY2025, all uncoded.</t>
         </is>
       </c>
     </row>
@@ -3756,7 +4859,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Rank</t>
@@ -8062,6 +9165,2736 @@
       </c>
       <c r="J113" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>As quoted</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Re-derived now</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Comes from</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery total funding FY2021-FY2025</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>266033307</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>266033307</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery distinct grants</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery award-years</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery distinct R01 grants</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery R01 award-years</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery would rank 1st of 119 on funding</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>1 of 119</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>1 of 119</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery would rank 2nd on distinct R01s</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery would rank 1st on R01 award-years</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>MGB Surgery would rank 1st on grant count</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Duke surgery funding</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>220811823</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>220811823</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Duke surgery rank</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Duke surgery distinct grants</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Duke surgery distinct R01s</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>WashU St. Louis surgery funding</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>154066689</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>154066689</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>WashU St. Louis surgery rank</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>WashU St. Louis surgery distinct grants</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>WashU St. Louis surgery distinct R01s</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Michigan surgery funding</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>131746006</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>131746006</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Michigan surgery rank</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Michigan surgery distinct grants</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Michigan surgery distinct R01s</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Massachusetts General Hospital surgery funding</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>160711713</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>160711713</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Massachusetts General Hospital surgery rank</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Massachusetts General Hospital surgery distinct grants</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Massachusetts General Hospital surgery distinct R01s</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Brigham and Women's Hospital surgery funding</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>105321594</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>105321594</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Brigham and Women's Hospital surgery rank</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Brigham and Women's Hospital surgery distinct grants</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Brigham and Women's Hospital surgery distinct R01s</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>MGH + BWH award-years sum to MGB's</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>MGH + BWH funding sums to MGB's</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>266033307</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>266033307</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>MGB total NIH FY2021-FY2025 ($5.11B)</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>5.107</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>5.107</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/rank_institution_FY2021_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>MGB total NIH FY2025 ($1.05B)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/rank_institution_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Johns Hopkins FY2021-FY2025 ($4.13B)</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>4.129</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>4.129</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/rank_institution_FY2021_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>MGB is 1st nationally only as a roll-up</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/rank_institution_FY2021_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>MGH alone ranks 7th nationally</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/rank_institution_FY2021_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>BWH alone ranks 22nd nationally</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/rank_institution_FY2021_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>MGB Medicine FY2021-FY2025 ($1.66B)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>1658.1</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>1658.1</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/mgb_departments_all.csv</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>no M-series activity code exists FY2021-FY2025</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>data/processed/award_years_annotated.parquet</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>no award-year is in mechanism family M</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>data/processed/award_years_annotated.parquet</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Blue Ridge institutions in their FY2025 surgery table</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>of those, paired to a figure here</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>agree to the dollar, as awarded</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>agree to within 1%, as awarded</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>agree to the dollar under BRIMR's conventions</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>WASHINGTON UNIVERSITY ST LOUIS matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>31820064</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>31820064</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>31820064</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>31820064</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF CALIFORNIA SAN FRANCISCO matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>27918696</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>27918696</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>27918696</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>27918696</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>STANFORD UNIVERSITY matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>17940324</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>17940324</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>17940324</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>17940324</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF MINNESOTA matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>16514952</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>16514952</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>16514952</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>16514952</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>JOHNS HOPKINS UNIVERSITY matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>12290262</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>12290262</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>12290262</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>12290262</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>COLUMBIA UNIVERSITY HEALTH SCIENCES matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>11205970</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>11205970</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>11205970</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>11205970</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>CORNELL UNIVERSITY WEILL MEDICAL COLLEGE matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>10000633</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>10000633</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>10000633</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>10000633</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF NORTH CAROLINA CHAPEL HILL matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>7865510</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>7865510</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>7865510</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>7865510</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>RUTGERS, THE STATE UNIVERSITY OF NEW JERSEY matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>7245955</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>7245955</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>7245955</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>7245955</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>INDIANA UNIVERSITY matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>6633379</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>6633379</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>6633379</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>6633379</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF TEXAS SOUTHWESTERN DALLAS matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>5144776</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>5144776</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>5144776</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>5144776</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF CALIFORNIA LOS ANGELES matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>7314362</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>7314362</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>7314362</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>7314362</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF CALIFORNIA SAN DIEGO matches Blue Ridge to the dollar</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>9176097</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>9176097</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ... and Blue Ridge itself says</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>9176097</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>9176097</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>DUKE UNIVERSITY differs by $15,375</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>15375</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>15375</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>UNIVERSITY OF MICHIGAN ANN ARBOR differs by $-10,795</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>-10795</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>-10795</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>MGH Surgery, published NIH figure for 2024</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>35000000</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>35000000</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/self_reported_departments_v1.csv</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>MGH Surgery, this analysis FY2024</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>30750166</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>30750166</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_self_reported.csv</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>MGH recovery</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/external_benchmark_self_reported.csv</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>MGH total research expenditures 2024</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>74000000</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>74000000</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/self_reported_departments_v1.csv</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>NIH is 47% of MGH Surgery research spending</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/self_reported_departments_v1.csv</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Blue Ridge Vanderbilt surgery FY2025</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>14408389</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>14408389</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>reference/external/brimr_surgery_2025.csv</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>NIH-coded Vanderbilt University surgery FY2025</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>336630</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>336630</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>data/processed/award_years_annotated.parquet</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>VUMC reconstruction FY2025</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>10858628</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>10858628</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>data/processed/pi_departments.parquet</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Vanderbilt recovery, coded + reconstructed over BRIMR total</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>derived from the three rows above</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>NOT the figure to quote: reconstruction alone over BRIMR total</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>75.36</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>75.36</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>derived; kept here so the two cannot be confused</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>ranked departments in the surgery table</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 sheet: reconstructed hospitals, excluding the roll-up</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 sheet: shaded rows including the roll-up</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>five-year sheet: reconstructed hospitals, excluding the roll-up</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>outputs/tables/surgery_ranking_with_mgb_FY2021_FY2025_corroborated.csv</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>uncoded recipients profiled</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>data/processed/pi_departments.parquet</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Bytes</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Retrieved</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER RePORTER_PRJ_C_FY2021.csv</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>63338049</v>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>aa8c596afa6b2c671e270ae700bf32691e7d5094ceb1130d0af1baeccea94457</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/exporter/projects/download/2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER RePORTER_PRJ_C_FY2022.csv</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>65876034</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>5ae867a9ba8b20c00f67b5d96fc890b29eada6331fd1a2d629b639786d3ae1f9</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/exporter/projects/download/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER RePORTER_PRJ_C_FY2023.csv</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>67964676</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>dac83610346e0f1d08c5ff763ae813179961faaf4f42c6908ceec407cc04629d</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/exporter/projects/download/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER RePORTER_PRJ_C_FY2024.csv</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>67364666</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>4a7b69091dae4ca75ad7447ed3a75f7344911d6dffd719d066102ef818547bab</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/exporter/projects/download/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>NIH ExPORTER RePORTER_PRJ_C_FY2025.csv</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>62152129</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>feab4e89ef7e04d3a76c62a95964730a52eb77f8c8914b9dede2be72f92313d7</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/exporter/projects/download/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>BRIMR rankings of NIH funding in 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Surgery table, 75 institutions</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>14834</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>712a7afcba5f6d1749618cd96f29041127fa9f63f97d89278159af3f7456f113</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>https://brimr.org/brimr-rankings-of-nih-funding-in-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>MGH Department of Surgery research figures</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>"Our research program in 2024"</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>https://www.massgeneral.org/surgery/research</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>PubMed / NCBI E-utilities</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>6,927 investigator profiles across 27 uncoded recipients</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>https://eutils.ncbi.nlm.nih.gov/entrez/eutils</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>This analysis: code, tables and figures</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>every number regenerable from the archived sources</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/AniruthAnanth/nih-funding-explorer</t>
+        </is>
       </c>
     </row>
   </sheetData>
